--- a/examples/data/sample_weather.xlsx
+++ b/examples/data/sample_weather.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\py-eto\examples\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDC4E4F-BBD9-478C-AB66-3580129284DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ED12A9-47F0-4C9F-8095-9E8DDC6D7BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28140" yWindow="7310" windowWidth="12000" windowHeight="12920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24900" yWindow="2880" windowWidth="16880" windowHeight="12920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>No</t>
   </si>
@@ -40,6 +41,24 @@
   </si>
   <si>
     <t>Latitude</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Elevation</t>
+  </si>
+  <si>
+    <t>RH_max</t>
+  </si>
+  <si>
+    <t>RH_min</t>
+  </si>
+  <si>
+    <t>u2</t>
+  </si>
+  <si>
+    <t>Rs</t>
   </si>
 </sst>
 </file>
@@ -910,4 +929,945 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7AF93F-A300-4E79-8C95-36B5B9F96240}">
+  <dimension ref="A1:J32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2">
+        <v>218</v>
+      </c>
+      <c r="C2">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D2">
+        <v>65</v>
+      </c>
+      <c r="E2">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="F2">
+        <v>23.4</v>
+      </c>
+      <c r="G2">
+        <v>71.3</v>
+      </c>
+      <c r="H2">
+        <v>25.3</v>
+      </c>
+      <c r="I2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>219</v>
+      </c>
+      <c r="C3">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D3">
+        <v>65</v>
+      </c>
+      <c r="E3">
+        <v>38.4</v>
+      </c>
+      <c r="F3">
+        <v>23.5</v>
+      </c>
+      <c r="G3">
+        <v>71.2</v>
+      </c>
+      <c r="H3">
+        <v>25.2</v>
+      </c>
+      <c r="I3">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4">
+        <v>220</v>
+      </c>
+      <c r="C4">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D4">
+        <v>65</v>
+      </c>
+      <c r="E4">
+        <v>38.5</v>
+      </c>
+      <c r="F4">
+        <v>23.6</v>
+      </c>
+      <c r="G4">
+        <v>71.099999999999994</v>
+      </c>
+      <c r="H4">
+        <v>25.1</v>
+      </c>
+      <c r="I4">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2025</v>
+      </c>
+      <c r="B5">
+        <v>221</v>
+      </c>
+      <c r="C5">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D5">
+        <v>65</v>
+      </c>
+      <c r="E5">
+        <v>38.6</v>
+      </c>
+      <c r="F5">
+        <v>23.7</v>
+      </c>
+      <c r="G5">
+        <v>71</v>
+      </c>
+      <c r="H5">
+        <v>25</v>
+      </c>
+      <c r="I5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2025</v>
+      </c>
+      <c r="B6">
+        <v>222</v>
+      </c>
+      <c r="C6">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D6">
+        <v>65</v>
+      </c>
+      <c r="E6">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="F6">
+        <v>23.8</v>
+      </c>
+      <c r="G6">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="H6">
+        <v>24.9</v>
+      </c>
+      <c r="I6">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2025</v>
+      </c>
+      <c r="B7">
+        <v>223</v>
+      </c>
+      <c r="C7">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D7">
+        <v>65</v>
+      </c>
+      <c r="E7">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="F7">
+        <v>23.9</v>
+      </c>
+      <c r="G7">
+        <v>70.8</v>
+      </c>
+      <c r="H7">
+        <v>24.8</v>
+      </c>
+      <c r="I7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2025</v>
+      </c>
+      <c r="B8">
+        <v>224</v>
+      </c>
+      <c r="C8">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D8">
+        <v>65</v>
+      </c>
+      <c r="E8">
+        <v>38.9</v>
+      </c>
+      <c r="F8">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>70.7</v>
+      </c>
+      <c r="H8">
+        <v>24.7</v>
+      </c>
+      <c r="I8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="B9">
+        <v>225</v>
+      </c>
+      <c r="C9">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D9">
+        <v>65</v>
+      </c>
+      <c r="E9">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>24.1</v>
+      </c>
+      <c r="G9">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="H9">
+        <v>24.6</v>
+      </c>
+      <c r="I9">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2025</v>
+      </c>
+      <c r="B10">
+        <v>226</v>
+      </c>
+      <c r="C10">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D10">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <v>39.1</v>
+      </c>
+      <c r="F10">
+        <v>24.2</v>
+      </c>
+      <c r="G10">
+        <v>70.5</v>
+      </c>
+      <c r="H10">
+        <v>24.5</v>
+      </c>
+      <c r="I10">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2025</v>
+      </c>
+      <c r="B11">
+        <v>227</v>
+      </c>
+      <c r="C11">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D11">
+        <v>65</v>
+      </c>
+      <c r="E11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="F11">
+        <v>24.3</v>
+      </c>
+      <c r="G11">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="H11">
+        <v>24.4</v>
+      </c>
+      <c r="I11">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2025</v>
+      </c>
+      <c r="B12">
+        <v>228</v>
+      </c>
+      <c r="C12">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D12">
+        <v>65</v>
+      </c>
+      <c r="E12">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="F12">
+        <v>24.4</v>
+      </c>
+      <c r="G12">
+        <v>70.300000000000097</v>
+      </c>
+      <c r="H12">
+        <v>24.3</v>
+      </c>
+      <c r="I12">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>2025</v>
+      </c>
+      <c r="B13">
+        <v>229</v>
+      </c>
+      <c r="C13">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D13">
+        <v>65</v>
+      </c>
+      <c r="E13">
+        <v>39.4</v>
+      </c>
+      <c r="F13">
+        <v>24.5</v>
+      </c>
+      <c r="G13">
+        <v>70.200000000000102</v>
+      </c>
+      <c r="H13">
+        <v>24.2</v>
+      </c>
+      <c r="I13">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>2025</v>
+      </c>
+      <c r="B14">
+        <v>230</v>
+      </c>
+      <c r="C14">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D14">
+        <v>65</v>
+      </c>
+      <c r="E14">
+        <v>39.5</v>
+      </c>
+      <c r="F14">
+        <v>24.6</v>
+      </c>
+      <c r="G14">
+        <v>70.100000000000094</v>
+      </c>
+      <c r="H14">
+        <v>24.1</v>
+      </c>
+      <c r="I14">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>2025</v>
+      </c>
+      <c r="B15">
+        <v>231</v>
+      </c>
+      <c r="C15">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D15">
+        <v>65</v>
+      </c>
+      <c r="E15">
+        <v>39.6</v>
+      </c>
+      <c r="F15">
+        <v>24.7</v>
+      </c>
+      <c r="G15">
+        <v>70.000000000000099</v>
+      </c>
+      <c r="H15">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>2025</v>
+      </c>
+      <c r="B16">
+        <v>232</v>
+      </c>
+      <c r="C16">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D16">
+        <v>65</v>
+      </c>
+      <c r="E16">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="F16">
+        <v>24.8</v>
+      </c>
+      <c r="G16">
+        <v>69.900000000000105</v>
+      </c>
+      <c r="H16">
+        <v>23.9</v>
+      </c>
+      <c r="I16">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>2025</v>
+      </c>
+      <c r="B17">
+        <v>233</v>
+      </c>
+      <c r="C17">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D17">
+        <v>65</v>
+      </c>
+      <c r="E17">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="F17">
+        <v>24.9</v>
+      </c>
+      <c r="G17">
+        <v>69.800000000000097</v>
+      </c>
+      <c r="H17">
+        <v>23.8</v>
+      </c>
+      <c r="I17">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>2025</v>
+      </c>
+      <c r="B18">
+        <v>234</v>
+      </c>
+      <c r="C18">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D18">
+        <v>65</v>
+      </c>
+      <c r="E18">
+        <v>39.9</v>
+      </c>
+      <c r="F18">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>69.700000000000102</v>
+      </c>
+      <c r="H18">
+        <v>23.7</v>
+      </c>
+      <c r="I18">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2025</v>
+      </c>
+      <c r="B19">
+        <v>235</v>
+      </c>
+      <c r="C19">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D19">
+        <v>65</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>25.1</v>
+      </c>
+      <c r="G19">
+        <v>69.600000000000094</v>
+      </c>
+      <c r="H19">
+        <v>23.6</v>
+      </c>
+      <c r="I19">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>2025</v>
+      </c>
+      <c r="B20">
+        <v>236</v>
+      </c>
+      <c r="C20">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D20">
+        <v>65</v>
+      </c>
+      <c r="E20">
+        <v>40.1</v>
+      </c>
+      <c r="F20">
+        <v>25.2</v>
+      </c>
+      <c r="G20">
+        <v>69.500000000000099</v>
+      </c>
+      <c r="H20">
+        <v>23.5</v>
+      </c>
+      <c r="I20">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>2025</v>
+      </c>
+      <c r="B21">
+        <v>237</v>
+      </c>
+      <c r="C21">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D21">
+        <v>65</v>
+      </c>
+      <c r="E21">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="F21">
+        <v>25.3</v>
+      </c>
+      <c r="G21">
+        <v>69.400000000000105</v>
+      </c>
+      <c r="H21">
+        <v>23.4</v>
+      </c>
+      <c r="I21">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2025</v>
+      </c>
+      <c r="B22">
+        <v>238</v>
+      </c>
+      <c r="C22">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D22">
+        <v>65</v>
+      </c>
+      <c r="E22">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="F22">
+        <v>25.4</v>
+      </c>
+      <c r="G22">
+        <v>69.300000000000097</v>
+      </c>
+      <c r="H22">
+        <v>23.3</v>
+      </c>
+      <c r="I22">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>2025</v>
+      </c>
+      <c r="B23">
+        <v>239</v>
+      </c>
+      <c r="C23">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D23">
+        <v>65</v>
+      </c>
+      <c r="E23">
+        <v>40.4</v>
+      </c>
+      <c r="F23">
+        <v>25.5</v>
+      </c>
+      <c r="G23">
+        <v>69.200000000000102</v>
+      </c>
+      <c r="H23">
+        <v>23.2</v>
+      </c>
+      <c r="I23">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>2025</v>
+      </c>
+      <c r="B24">
+        <v>240</v>
+      </c>
+      <c r="C24">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D24">
+        <v>65</v>
+      </c>
+      <c r="E24">
+        <v>40.5</v>
+      </c>
+      <c r="F24">
+        <v>25.6</v>
+      </c>
+      <c r="G24">
+        <v>69.100000000000094</v>
+      </c>
+      <c r="H24">
+        <v>23.1</v>
+      </c>
+      <c r="I24">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>2025</v>
+      </c>
+      <c r="B25">
+        <v>241</v>
+      </c>
+      <c r="C25">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D25">
+        <v>65</v>
+      </c>
+      <c r="E25">
+        <v>40.6</v>
+      </c>
+      <c r="F25">
+        <v>25.7</v>
+      </c>
+      <c r="G25">
+        <v>69.000000000000099</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>2025</v>
+      </c>
+      <c r="B26">
+        <v>242</v>
+      </c>
+      <c r="C26">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D26">
+        <v>65</v>
+      </c>
+      <c r="E26">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="F26">
+        <v>25.8</v>
+      </c>
+      <c r="G26">
+        <v>68.900000000000105</v>
+      </c>
+      <c r="H26">
+        <v>22.9</v>
+      </c>
+      <c r="I26">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>2025</v>
+      </c>
+      <c r="B27">
+        <v>243</v>
+      </c>
+      <c r="C27">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D27">
+        <v>65</v>
+      </c>
+      <c r="E27">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F27">
+        <v>25.9</v>
+      </c>
+      <c r="G27">
+        <v>68.800000000000097</v>
+      </c>
+      <c r="H27">
+        <v>22.8</v>
+      </c>
+      <c r="I27">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>2025</v>
+      </c>
+      <c r="B28">
+        <v>244</v>
+      </c>
+      <c r="C28">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D28">
+        <v>65</v>
+      </c>
+      <c r="E28">
+        <v>40.9</v>
+      </c>
+      <c r="F28">
+        <v>26</v>
+      </c>
+      <c r="G28">
+        <v>68.700000000000102</v>
+      </c>
+      <c r="H28">
+        <v>22.7</v>
+      </c>
+      <c r="I28">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2025</v>
+      </c>
+      <c r="B29">
+        <v>245</v>
+      </c>
+      <c r="C29">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D29">
+        <v>65</v>
+      </c>
+      <c r="E29">
+        <v>41</v>
+      </c>
+      <c r="F29">
+        <v>26.1</v>
+      </c>
+      <c r="G29">
+        <v>68.600000000000193</v>
+      </c>
+      <c r="H29">
+        <v>22.6</v>
+      </c>
+      <c r="I29">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>2025</v>
+      </c>
+      <c r="B30">
+        <v>246</v>
+      </c>
+      <c r="C30">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D30">
+        <v>65</v>
+      </c>
+      <c r="E30">
+        <v>41.1</v>
+      </c>
+      <c r="F30">
+        <v>26.2</v>
+      </c>
+      <c r="G30">
+        <v>68.500000000000199</v>
+      </c>
+      <c r="H30">
+        <v>22.5</v>
+      </c>
+      <c r="I30">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>2025</v>
+      </c>
+      <c r="B31">
+        <v>247</v>
+      </c>
+      <c r="C31">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D31">
+        <v>65</v>
+      </c>
+      <c r="E31">
+        <v>41.2</v>
+      </c>
+      <c r="F31">
+        <v>26.3</v>
+      </c>
+      <c r="G31">
+        <v>68.400000000000205</v>
+      </c>
+      <c r="H31">
+        <v>22.4</v>
+      </c>
+      <c r="I31">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>2025</v>
+      </c>
+      <c r="B32">
+        <v>248</v>
+      </c>
+      <c r="C32">
+        <v>37.365886000000003</v>
+      </c>
+      <c r="D32">
+        <v>65</v>
+      </c>
+      <c r="E32">
+        <v>41.3</v>
+      </c>
+      <c r="F32">
+        <v>26.4</v>
+      </c>
+      <c r="G32">
+        <v>68.300000000000196</v>
+      </c>
+      <c r="H32">
+        <v>22.3</v>
+      </c>
+      <c r="I32">
+        <v>1.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/examples/data/sample_weather.xlsx
+++ b/examples/data/sample_weather.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\py-eto\examples\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17550889-670A-48FD-932D-D2A49363AC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93368DAB-7C06-4749-B722-E9597FB2C451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40850" yWindow="2240" windowWidth="12220" windowHeight="18700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30910" yWindow="0" windowWidth="10140" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>No</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>G</t>
+  </si>
+  <si>
+    <t>Rn</t>
   </si>
 </sst>
 </file>
@@ -950,10 +953,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C7AF93F-A300-4E79-8C95-36B5B9F96240}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -990,8 +993,11 @@
       <c r="L1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -1030,8 +1036,11 @@
       <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M2">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -1070,8 +1079,11 @@
       <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M3">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -1110,8 +1122,11 @@
       <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M4">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -1150,8 +1165,11 @@
       <c r="L5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M5">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -1190,8 +1208,11 @@
       <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M6">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2025</v>
       </c>
@@ -1230,8 +1251,11 @@
       <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M7">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2025</v>
       </c>
@@ -1270,8 +1294,11 @@
       <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M8">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2025</v>
       </c>
@@ -1310,8 +1337,11 @@
       <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M9">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2025</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="L10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M10">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -1390,8 +1423,11 @@
       <c r="L11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M11">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2025</v>
       </c>
@@ -1430,8 +1466,11 @@
       <c r="L12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M12">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2025</v>
       </c>
@@ -1470,8 +1509,11 @@
       <c r="L13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M13">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2025</v>
       </c>
@@ -1510,8 +1552,11 @@
       <c r="L14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M14">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2025</v>
       </c>
@@ -1550,8 +1595,11 @@
       <c r="L15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M15">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2025</v>
       </c>
@@ -1590,8 +1638,11 @@
       <c r="L16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M16">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2025</v>
       </c>
@@ -1630,8 +1681,11 @@
       <c r="L17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M17">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2025</v>
       </c>
@@ -1670,8 +1724,11 @@
       <c r="L18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M18">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2025</v>
       </c>
@@ -1710,8 +1767,11 @@
       <c r="L19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M19">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2025</v>
       </c>
@@ -1750,8 +1810,11 @@
       <c r="L20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M20">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2025</v>
       </c>
@@ -1790,8 +1853,11 @@
       <c r="L21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M21">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2025</v>
       </c>
@@ -1830,8 +1896,11 @@
       <c r="L22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M22">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2025</v>
       </c>
@@ -1870,8 +1939,11 @@
       <c r="L23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M23">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2025</v>
       </c>
@@ -1910,8 +1982,11 @@
       <c r="L24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M24">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2025</v>
       </c>
@@ -1950,8 +2025,11 @@
       <c r="L25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M25">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2025</v>
       </c>
@@ -1990,8 +2068,11 @@
       <c r="L26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M26">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2025</v>
       </c>
@@ -2030,8 +2111,11 @@
       <c r="L27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M27">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2025</v>
       </c>
@@ -2070,8 +2154,11 @@
       <c r="L28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M28">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2025</v>
       </c>
@@ -2110,8 +2197,11 @@
       <c r="L29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M29">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2025</v>
       </c>
@@ -2150,8 +2240,11 @@
       <c r="L30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M30">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2025</v>
       </c>
@@ -2190,8 +2283,11 @@
       <c r="L31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M31">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2025</v>
       </c>
@@ -2229,6 +2325,9 @@
       </c>
       <c r="L32">
         <v>0</v>
+      </c>
+      <c r="M32">
+        <v>4520</v>
       </c>
     </row>
   </sheetData>
